--- a/reports/2026-10-25_report.xlsx
+++ b/reports/2026-10-25_report.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -598,26 +598,26 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0.6182197989923358</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.4243396623216969</v>
+        <v>0.4214723950998298</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.1938801366706389</v>
+        <v>0.196747403892506</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.4342699336622189</v>
+        <v>0.4404521316521426</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -666,26 +666,26 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Tipico</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>0.371543748692694</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.1979033636431637</v>
+        <v>0.1944329547217231</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.1736403850495302</v>
+        <v>0.1771107939709709</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.9320274932020087</v>
+        <v>1.006336242940547</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0.481741624564035</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.3114351718778278</v>
+        <v>0.3148030544269839</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1703064526862072</v>
+        <v>0.1669385701370511</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.5030338686397893</v>
+        <v>0.4789467874115874</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>2.72</v>
+        <v>1.85</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -821,11 +821,11 @@
         <v>0.1482962958488019</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -835,65 +835,65 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>roma</t>
+          <t>paris saint germain</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Away (2)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Nordic Bet</t>
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2.21</v>
+        <v>7.1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.5663856748812703</v>
+        <v>0.2732324731826497</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.4429935665194775</v>
+        <v>0.1453255593905549</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1233921083617928</v>
+        <v>0.1279069137920948</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2517123414876075</v>
+        <v>0.9399505595968127</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>3.63</v>
+        <v>1.85</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -903,65 +903,65 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>paris saint germain</t>
+          <t>roma</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BetOnline.ag</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>6.95</v>
+        <v>2.21</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.2732324731826497</v>
+        <v>0.5663856748812703</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1506068410186629</v>
+        <v>0.4429935665194775</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1226256321639868</v>
+        <v>0.1233921083617928</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.8989656886194155</v>
+        <v>0.2517123414876075</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>2.72</v>
+        <v>3.49</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1001,31 +1001,31 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>William Hill</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.7775009235052397</v>
+        <v>0.5991384423493973</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.6584233068844428</v>
+        <v>0.4760053382706315</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1190776166207969</v>
+        <v>0.1231331040787658</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1196013298475451</v>
+        <v>0.2581907289337344</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
@@ -1039,65 +1039,65 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>hearts</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>rangers</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Unibet (NL)</t>
+          <t>Betsson</t>
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>3.2</v>
+        <v>1.45</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.4052557017259494</v>
+        <v>0.7775009235052397</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2963561378509337</v>
+        <v>0.6555057877689695</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1088995638750156</v>
+        <v>0.1219951357362702</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2968182455230381</v>
+        <v>0.1273763390825975</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>3.63</v>
+        <v>2.62</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -1107,65 +1107,65 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>hearts</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>rangers</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Unibet (NL)</t>
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5832385716732491</v>
+        <v>0.4052557017259494</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.4745497423914363</v>
+        <v>0.2963561378509337</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1086888292818128</v>
+        <v>0.1088995638750156</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2131362290803582</v>
+        <v>0.2968182455230381</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>2.72</v>
+        <v>3.49</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -1180,22 +1180,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1210,26 +1210,26 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.08</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5991384423493973</v>
+        <v>0.5832385716732491</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4904795922036871</v>
+        <v>0.4749808089094593</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1086588501457101</v>
+        <v>0.1082577627637898</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2462079600867464</v>
+        <v>0.2131362290803582</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -1288,16 +1288,16 @@
         <v>0.8052896418513827</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.7057032142782423</v>
+        <v>0.7064977647914527</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0995864275731404</v>
+        <v>0.09879187705993009</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0.1032468093363945</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
@@ -1356,16 +1356,16 @@
         <v>0.4846715655705451</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3910575241116682</v>
+        <v>0.3930568772200054</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.09361404145887692</v>
+        <v>0.09161468835053965</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0.2213723452377736</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
@@ -1384,60 +1384,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>inter milan</t>
+          <t>estoril</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>moreirense</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Away (2)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Betsson</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.42</v>
+        <v>4.74</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.7643877239917715</v>
+        <v>0.3084039729250643</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6738759091727832</v>
+        <v>0.2173310516300578</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.09051181481898829</v>
+        <v>0.09107292129500652</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.08543056806831539</v>
+        <v>0.4618348316648049</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>2.72</v>
+        <v>3.49</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>BetOnline.ag</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="J15" s="3" t="n">
@@ -1492,16 +1492,16 @@
         <v>0.5284455777634646</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.4407262614365446</v>
+        <v>0.4413869969669937</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.08771931632691998</v>
+        <v>0.08705858079647083</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>0.1731491826348914</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>3.63</v>
+        <v>3.49</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
@@ -1520,60 +1520,60 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>manchester united</t>
+          <t>inter milan</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>William Hill</t>
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.501357962711886</v>
+        <v>0.7643877239917715</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.420207753326326</v>
+        <v>0.6786534295911641</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.08115020938556006</v>
+        <v>0.08573429440060731</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1932319512542888</v>
+        <v>0.07014281358848007</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>3.63</v>
+        <v>2.62</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1598,46 +1598,46 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>lorient</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Away (2)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.87</v>
+        <v>4.25</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.6101972364695072</v>
+        <v>0.3259077790138454</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5296610680550689</v>
+        <v>0.2440908735227083</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.08053616841443834</v>
+        <v>0.08181690549113713</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1410688321979785</v>
+        <v>0.3851080608088429</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1666,46 +1666,46 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>lorient</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.25</v>
+        <v>1.87</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.3259077790138454</v>
+        <v>0.6101972364695072</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2455319100286087</v>
+        <v>0.5294669686761869</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.08037586898523666</v>
+        <v>0.08073026779332027</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3851080608088429</v>
+        <v>0.1410688321979785</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
@@ -1724,60 +1724,60 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>manchester united</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Betsson</t>
+          <t>Unibet (NL)</t>
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4412516805372731</v>
+        <v>0.501357962711886</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3652929971328698</v>
+        <v>0.4241906930894931</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.07595868340440332</v>
+        <v>0.07716726962239295</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.1693169534237737</v>
+        <v>0.1631504734915756</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>2.72</v>
+        <v>3.49</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -1832,20 +1832,20 @@
         <v>0.8010754395599823</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.7258127722295252</v>
+        <v>0.7250307407688314</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.07526266733045706</v>
+        <v>0.07604469879115083</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0.04139807142797691</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>3.63</v>
+        <v>3.49</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -1855,27 +1855,27 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>inter milan</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1894,26 +1894,26 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.31</v>
+        <v>2.65</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7948945252539578</v>
+        <v>0.4412516805372731</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.7239742871521218</v>
+        <v>0.3652929971328698</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.07092023810183601</v>
+        <v>0.07595868340440332</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.04131182808268474</v>
+        <v>0.1693169534237737</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>2.72</v>
+        <v>3.49</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>inter milan</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1953,35 +1953,35 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Betsson</t>
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2.07</v>
+        <v>1.31</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5393476693683286</v>
+        <v>0.7948945252539578</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4737477184307387</v>
+        <v>0.7239742871521218</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.06559995093758986</v>
+        <v>0.07092023810183601</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.11644967559244</v>
+        <v>0.04131182808268474</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>3.63</v>
+        <v>2.62</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -1991,61 +1991,61 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>estoril</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>moreirense</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Tipico</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>4</v>
+        <v>2.07</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.3084039729250643</v>
+        <v>0.5393476693683286</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.2433721063493016</v>
+        <v>0.4737477184307387</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.06503186657576271</v>
+        <v>0.06559995093758986</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2336158917002573</v>
+        <v>0.11644967559244</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>3.54</v>
+        <v>3.49</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
@@ -2064,22 +2064,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>hull city</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2089,31 +2089,31 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Draw (X)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>BetAnything</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>8</v>
+        <v>4.23</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.2034314801583303</v>
+        <v>0.2972610717420113</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1392532417835651</v>
+        <v>0.2321631481010583</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.06417823837476522</v>
+        <v>0.06509792364095301</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.6274518412666426</v>
+        <v>0.2574143334687078</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>2.72</v>
+        <v>1.74</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2127,65 +2127,65 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>aberdeen</t>
+          <t>for sittard</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>falkirk</t>
+          <t>excelsior</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.72</v>
+        <v>1.76</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.3281718969442999</v>
+        <v>0.6213574486486763</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2644824236079591</v>
+        <v>0.5564864909435647</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.06368947333634073</v>
+        <v>0.06487095770511153</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2207994566327955</v>
+        <v>0.09358910962167033</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>3.63</v>
+        <v>2.72</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -2200,22 +2200,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>hull city</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>sp braga</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2225,35 +2225,35 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Draw (X)</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>4.25</v>
+        <v>6.83</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.2972610717420113</v>
+        <v>0.216953187415267</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2348209796475321</v>
+        <v>0.1521324132946012</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.06244009209447918</v>
+        <v>0.06482077412066584</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2633595549035479</v>
+        <v>0.4817902700462739</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>1.82</v>
+        <v>3.49</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -2298,30 +2298,30 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Tipico</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>0.5126619804804484</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4509016593404622</v>
+        <v>0.4488183943322583</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.0617603211399862</v>
+        <v>0.06384358614819013</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1278563570569866</v>
+        <v>0.1329829768617909</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>2.72</v>
+        <v>3.49</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -2331,27 +2331,27 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>gent</t>
+          <t>aberdeen</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>anderlecht</t>
+          <t>falkirk</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Away (2)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2370,22 +2370,22 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.36</v>
+        <v>3.72</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.4658645760359786</v>
+        <v>0.3281718969442999</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4053182123611488</v>
+        <v>0.2644539006529559</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0605463636748298</v>
+        <v>0.063717996291344</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.09944039944490957</v>
+        <v>0.2207994566327955</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>3.32</v>
+        <v>3.49</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
@@ -2444,16 +2444,16 @@
         <v>0.2993798442859898</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.2421189725232363</v>
+        <v>0.239926817338097</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.05726087176275352</v>
+        <v>0.05945302694789284</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.2603891444440172</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -2472,60 +2472,60 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>sp braga</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>Betsson</t>
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>6.25</v>
+        <v>1.32</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.216953187415267</v>
+        <v>0.78087790448716</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.160243976202629</v>
+        <v>0.7228476869170627</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.05670921121263806</v>
+        <v>0.0580302175700973</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.3559574213454191</v>
+        <v>0.03075883392305134</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap</t>
         </is>
       </c>
     </row>
@@ -2540,22 +2540,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>club brugge</t>
+          <t>for sittard</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>st truiden</t>
+          <t>excelsior</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2570,30 +2570,30 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.36</v>
+        <v>2.71</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.7520420956786665</v>
+        <v>0.4156544274247579</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.6969049692474001</v>
+        <v>0.3595033492136283</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.05513712643126645</v>
+        <v>0.05615107821112969</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.02277725012298659</v>
+        <v>0.1264234983210941</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>2.87</v>
+        <v>2.51</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap</t>
         </is>
       </c>
     </row>
@@ -2608,60 +2608,60 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>for sittard</t>
+          <t>gent</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>excelsior</t>
+          <t>anderlecht</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.71</v>
+        <v>2.35</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.6213574486486763</v>
+        <v>0.4658645760359786</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.5664536154159017</v>
+        <v>0.4102233486507934</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.05490383323277459</v>
+        <v>0.05564122738518529</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.0625212371892363</v>
+        <v>0.09478175368454989</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>3.63</v>
+        <v>3.06</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sassuolo</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2701,31 +2701,31 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>GTbets</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2.46</v>
+        <v>7.5</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.4568698492465614</v>
+        <v>0.2034314801583303</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.4020234158769529</v>
+        <v>0.1478016389739719</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.05484643336960848</v>
+        <v>0.05562984118435838</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.123899829146541</v>
+        <v>0.5257361011874775</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>0.6088398188105031</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.5543426746953728</v>
+        <v>0.5560223970412344</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.05449714411513029</v>
+        <v>0.05281742176926874</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>0.1020000720470107</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>3.63</v>
+        <v>3.49</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
@@ -2812,60 +2812,196 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>club brugge</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>st truiden</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Home (1)</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>1xBet</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0.7520420956786665</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0.6996566542313409</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>0.0523854414473256</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>0.02277725012298659</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Away (2)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Codere (IT)</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.6830579834855618</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0.6310515453127501</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>0.0520064381728117</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0.05190929456776527</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>France Ligue 1</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>paris saint germain</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Home (1)</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>1xBet</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>0.680156878514566</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>0.6290135236880946</v>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>0.05114335482647137</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>0.06784629926786856</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Draw (X)</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>0.2289518790465764</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>0.1783666016591509</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>0.05058527738742552</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>0.3141837857273484</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap</t>
         </is>
       </c>
     </row>
@@ -3032,25 +3168,25 @@
         <v>0.3795275205934532</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3312712901628174</v>
+        <v>0.3334261411251531</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.04825623043063582</v>
+        <v>0.04610137946830017</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>22</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>0.05821879023753829</v>
+        <v>0.05838785748437444</v>
       </c>
     </row>
     <row r="3">
@@ -3095,25 +3231,25 @@
         <v>0.2505928277924926</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2629487752621829</v>
+        <v>0.2628210827955617</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="N3" s="6" t="n">
-        <v>-0.01235594746969026</v>
+        <v>-0.01222825500306912</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>22</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0.05821879023753829</v>
+        <v>0.05838785748437444</v>
       </c>
     </row>
     <row r="4">
@@ -3158,10 +3294,10 @@
         <v>0.3698796516140541</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.4057799345749997</v>
+        <v>0.4037527760792852</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -3169,14 +3305,14 @@
         </is>
       </c>
       <c r="N4" s="6" t="n">
-        <v>-0.03590028296094561</v>
+        <v>-0.03387312446523111</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>22</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>0.05821879023753829</v>
+        <v>0.05838785748437444</v>
       </c>
     </row>
     <row r="5">
@@ -3347,18 +3483,18 @@
         <v>0.371543748692694</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1979033636431637</v>
+        <v>0.1944329547217231</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Tipico</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1736403850495302</v>
+        <v>0.1771107939709709</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -3369,7 +3505,7 @@
         <v>22</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.05805438389092082</v>
+        <v>0.05618853196718426</v>
       </c>
     </row>
     <row r="8">
@@ -3414,18 +3550,18 @@
         <v>0.2972610717420113</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2348209796475321</v>
+        <v>0.2321631481010583</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>BetAnything</t>
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.06244009209447918</v>
+        <v>0.06509792364095301</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -3436,7 +3572,7 @@
         <v>22</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.05805438389092082</v>
+        <v>0.05618853196718426</v>
       </c>
     </row>
     <row r="9">
@@ -3481,7 +3617,7 @@
         <v>0.3311951795652948</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.5672756567093041</v>
+        <v>0.5734038971772187</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>1.73</v>
@@ -3492,14 +3628,14 @@
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>-0.2360804771440093</v>
+        <v>-0.2422087176119239</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>22</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0.05805438389092082</v>
+        <v>0.05618853196718426</v>
       </c>
     </row>
     <row r="10">
@@ -3544,7 +3680,7 @@
         <v>0.3817802010076642</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.575660337678303</v>
+        <v>0.5785276049001702</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>1.71</v>
@@ -3555,14 +3691,14 @@
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>-0.1938801366706389</v>
+        <v>-0.196747403892506</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>13</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>0.06197138344565048</v>
+        <v>0.06233045939573086</v>
       </c>
     </row>
     <row r="11">
@@ -3607,18 +3743,18 @@
         <v>0.6182197989923358</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4243396623216969</v>
+        <v>0.4214723950998298</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1938801366706389</v>
+        <v>0.196747403892506</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -3629,7 +3765,7 @@
         <v>13</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.06197138344565048</v>
+        <v>0.06233045939573086</v>
       </c>
     </row>
     <row r="12">
@@ -3674,18 +3810,18 @@
         <v>0.501357962711886</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.420207753326326</v>
+        <v>0.4241906930894931</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>Unibet (NL)</t>
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.08115020938556006</v>
+        <v>0.07716726962239295</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -3696,7 +3832,7 @@
         <v>22</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.05674305766257552</v>
+        <v>0.05729304592117911</v>
       </c>
     </row>
     <row r="13">
@@ -3741,7 +3877,7 @@
         <v>0.2342616597105691</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.2649348344929497</v>
+        <v>0.267219585691172</v>
       </c>
       <c r="L13" s="5" t="n">
         <v>3.74</v>
@@ -3752,14 +3888,14 @@
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>-0.03067317478238066</v>
+        <v>-0.0329579259806029</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>22</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>0.05674305766257552</v>
+        <v>0.05729304592117911</v>
       </c>
     </row>
     <row r="14">
@@ -3804,7 +3940,7 @@
         <v>0.2643803775775449</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.3148574121807243</v>
+        <v>0.3085897212193349</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>3.2</v>
@@ -3815,14 +3951,14 @@
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>-0.05047703460317937</v>
+        <v>-0.04420934364179002</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>22</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>0.05674305766257552</v>
+        <v>0.05729304592117911</v>
       </c>
     </row>
     <row r="15">
@@ -3867,7 +4003,7 @@
         <v>0.5948818661518259</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.5776536933649328</v>
+        <v>0.5718451118477063</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>1.71</v>
@@ -3878,14 +4014,14 @@
         </is>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.01722817278689315</v>
+        <v>0.02303675430411967</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>12</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>0.0610391333980686</v>
+        <v>0.06268762209709343</v>
       </c>
     </row>
     <row r="16">
@@ -3930,7 +4066,7 @@
         <v>0.4051181338481741</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.4223463066350672</v>
+        <v>0.4281548881522938</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>2.33</v>
@@ -3941,14 +4077,14 @@
         </is>
       </c>
       <c r="N16" s="6" t="n">
-        <v>-0.01722817278689315</v>
+        <v>-0.02303675430411972</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>12</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>0.0610391333980686</v>
+        <v>0.06268762209709343</v>
       </c>
     </row>
     <row r="17">
@@ -3993,25 +4129,25 @@
         <v>0.305626178709399</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.3201668028987701</v>
+        <v>0.3255460774078024</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N17" s="6" t="n">
-        <v>-0.01454062418937119</v>
+        <v>-0.01991989869840349</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>22</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0.05773623566456488</v>
+        <v>0.0578802499898152</v>
       </c>
     </row>
     <row r="18">
@@ -4056,25 +4192,25 @@
         <v>0.2968237102919514</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.2972057567080956</v>
+        <v>0.3021123797457567</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>GTbets</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N18" s="6" t="n">
-        <v>-0.0003820464161442549</v>
+        <v>-0.00528866945380535</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>22</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>0.05773623566456488</v>
+        <v>0.0578802499898152</v>
       </c>
     </row>
     <row r="19">
@@ -4119,25 +4255,25 @@
         <v>0.3975501109986497</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.3826274403931343</v>
+        <v>0.3723415428464408</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.01492267060551539</v>
+        <v>0.02520856815220884</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>22</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.05773623566456488</v>
+        <v>0.0578802499898152</v>
       </c>
     </row>
     <row r="20">
@@ -4182,25 +4318,25 @@
         <v>0.3911601811894969</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.4456573253046271</v>
+        <v>0.4439776029587657</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N20" s="6" t="n">
-        <v>-0.05449714411513029</v>
+        <v>-0.05281742176926885</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>16</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>0.05683999086728168</v>
+        <v>0.05685994331129547</v>
       </c>
     </row>
     <row r="21">
@@ -4245,7 +4381,7 @@
         <v>0.6088398188105031</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.5543426746953728</v>
+        <v>0.5560223970412344</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>1.81</v>
@@ -4256,7 +4392,7 @@
         </is>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.05449714411513029</v>
+        <v>0.05281742176926874</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -4267,7 +4403,7 @@
         <v>16</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.05683999086728168</v>
+        <v>0.05685994331129547</v>
       </c>
     </row>
     <row r="22">
@@ -4312,18 +4448,18 @@
         <v>0.5284455777634646</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4407262614365446</v>
+        <v>0.4413869969669937</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>2.22</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>BetOnline.ag</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.08771931632691998</v>
+        <v>0.08705858079647083</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -4334,7 +4470,7 @@
         <v>21</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.0635082966722883</v>
+        <v>0.061613887930638</v>
       </c>
     </row>
     <row r="23">
@@ -4379,7 +4515,7 @@
         <v>0.2313607222805535</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.2904481671564657</v>
+        <v>0.2918427849426076</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>3.45</v>
@@ -4390,14 +4526,14 @@
         </is>
       </c>
       <c r="N23" s="6" t="n">
-        <v>-0.05908744487591222</v>
+        <v>-0.06048206266205414</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>21</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.0635082966722883</v>
+        <v>0.061613887930638</v>
       </c>
     </row>
     <row r="24">
@@ -4442,25 +4578,25 @@
         <v>0.2401936999559821</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.2688255714069897</v>
+        <v>0.2667702180903986</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N24" s="6" t="n">
-        <v>-0.02863187145100765</v>
+        <v>-0.02657651813441653</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>21</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>0.0635082966722883</v>
+        <v>0.061613887930638</v>
       </c>
     </row>
     <row r="25">
@@ -4505,10 +4641,10 @@
         <v>0.4494124022041225</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.4853932679279125</v>
+        <v>0.4834551240356179</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -4516,14 +4652,14 @@
         </is>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.03598086572379</v>
+        <v>-0.03404272183149537</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>16</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.05858668495611841</v>
+        <v>0.05783458616774109</v>
       </c>
     </row>
     <row r="26">
@@ -4568,7 +4704,7 @@
         <v>0.5505875977958775</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.5146067320720875</v>
+        <v>0.5165448759643821</v>
       </c>
       <c r="L26" s="5" t="n">
         <v>1.9</v>
@@ -4579,14 +4715,14 @@
         </is>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.03598086572379</v>
+        <v>0.03404272183149537</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
         <v>16</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>0.05858668495611841</v>
+        <v>0.05783458616774109</v>
       </c>
     </row>
     <row r="27">
@@ -4631,7 +4767,7 @@
         <v>0.8052896418513827</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.7057032142782423</v>
+        <v>0.7064977647914527</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>1.37</v>
@@ -4642,7 +4778,7 @@
         </is>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.0995864275731404</v>
+        <v>0.09879187705993009</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -4653,7 +4789,7 @@
         <v>21</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.05997991332596563</v>
+        <v>0.05952342326403676</v>
       </c>
     </row>
     <row r="28">
@@ -4698,7 +4834,7 @@
         <v>0.1057792243589948</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.1717169327841999</v>
+        <v>0.1723936411992864</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>5.87</v>
@@ -4709,14 +4845,14 @@
         </is>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-0.06593770842520504</v>
+        <v>-0.06661441684029161</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
         <v>21</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>0.05997991332596563</v>
+        <v>0.05952342326403676</v>
       </c>
     </row>
     <row r="29">
@@ -4761,7 +4897,7 @@
         <v>0.08893113378962259</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.1225798529375578</v>
+        <v>0.121108594009261</v>
       </c>
       <c r="L29" s="5" t="n">
         <v>9</v>
@@ -4772,14 +4908,14 @@
         </is>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-0.03364871914793525</v>
+        <v>-0.03217746021963837</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
         <v>21</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>0.05997991332596563</v>
+        <v>0.05952342326403676</v>
       </c>
     </row>
     <row r="30">
@@ -4824,18 +4960,18 @@
         <v>0.7643877239917715</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.6738759091727832</v>
+        <v>0.6786534295911641</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Betsson</t>
+          <t>William Hill</t>
         </is>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.09051181481898829</v>
+        <v>0.08573429440060731</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -4846,7 +4982,7 @@
         <v>3</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.05499421451166405</v>
+        <v>0.05504661979692357</v>
       </c>
     </row>
     <row r="31">
@@ -4891,10 +5027,10 @@
         <v>0.2356122760082285</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.3261240908272168</v>
+        <v>0.321346570408836</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -4902,14 +5038,14 @@
         </is>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.09051181481898823</v>
+        <v>-0.08573429440060742</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
         <v>3</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>0.05499421451166405</v>
+        <v>0.05504661979692357</v>
       </c>
     </row>
     <row r="32">
@@ -4954,10 +5090,10 @@
         <v>0.2034314801583303</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.1392532417835651</v>
+        <v>0.1478016389739719</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -4965,7 +5101,7 @@
         </is>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.06417823837476522</v>
+        <v>0.05562984118435838</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -4976,7 +5112,7 @@
         <v>21</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.06148786238046162</v>
+        <v>0.06047328044779855</v>
       </c>
     </row>
     <row r="33">
@@ -5021,25 +5157,25 @@
         <v>0.2319966404025896</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.2255844157278786</v>
+        <v>0.2282471531279316</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.006412224674711003</v>
+        <v>0.003749487274657959</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
         <v>21</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>0.06148786238046162</v>
+        <v>0.06047328044779855</v>
       </c>
     </row>
     <row r="34">
@@ -5084,10 +5220,10 @@
         <v>0.5645718794390802</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.6351623424885564</v>
+        <v>0.6239512078980964</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -5095,14 +5231,14 @@
         </is>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.07059046304947625</v>
+        <v>-0.05937932845901628</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
         <v>21</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>0.06148786238046162</v>
+        <v>0.06047328044779855</v>
       </c>
     </row>
     <row r="35">
@@ -5147,10 +5283,10 @@
         <v>0.4008615576506027</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.5095204077963129</v>
+        <v>0.5239946617293685</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -5158,14 +5294,14 @@
         </is>
       </c>
       <c r="N35" s="6" t="n">
-        <v>-0.1086588501457103</v>
+        <v>-0.1231331040787658</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
         <v>16</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>0.05763714945577986</v>
+        <v>0.05677348586250211</v>
       </c>
     </row>
     <row r="36">
@@ -5210,18 +5346,18 @@
         <v>0.5991384423493973</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.4904795922036871</v>
+        <v>0.4760053382706315</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.1086588501457101</v>
+        <v>0.1231331040787658</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -5232,7 +5368,7 @@
         <v>16</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>0.05763714945577986</v>
+        <v>0.05677348586250211</v>
       </c>
     </row>
     <row r="37">
@@ -5277,25 +5413,25 @@
         <v>0.2437320414651176</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.2134371751538652</v>
+        <v>0.2124502449071045</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.03029486631125244</v>
+        <v>0.03128179655801316</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
         <v>21</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>0.06070831786187564</v>
+        <v>0.06059110270137406</v>
       </c>
     </row>
     <row r="38">
@@ -5340,25 +5476,25 @@
         <v>0.223460129531155</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.2608236340073519</v>
+        <v>0.2612418613104973</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>3.8</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>BetAnything</t>
         </is>
       </c>
       <c r="N38" s="6" t="n">
-        <v>-0.03736350447619688</v>
+        <v>-0.03778173177934227</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
         <v>21</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>0.06070831786187564</v>
+        <v>0.06059110270137406</v>
       </c>
     </row>
     <row r="39">
@@ -5403,7 +5539,7 @@
         <v>0.5328078290037275</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.525739190838783</v>
+        <v>0.5263078937823983</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>1.87</v>
@@ -5414,14 +5550,14 @@
         </is>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.007068638164944518</v>
+        <v>0.006499935221329189</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
         <v>21</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>0.06070831786187564</v>
+        <v>0.06059110270137406</v>
       </c>
     </row>
     <row r="40">
@@ -5466,7 +5602,7 @@
         <v>0.5100547751752695</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.5034699303199822</v>
+        <v>0.5003501004882048</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>1.97</v>
@@ -5477,14 +5613,14 @@
         </is>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.00658484485528732</v>
+        <v>0.009704674687064707</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
         <v>16</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>0.05858151479569788</v>
+        <v>0.05746773346165605</v>
       </c>
     </row>
     <row r="41">
@@ -5529,7 +5665,7 @@
         <v>0.4899452248247305</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.4965300696800177</v>
+        <v>0.4996498995117951</v>
       </c>
       <c r="L41" s="5" t="n">
         <v>1.97</v>
@@ -5540,14 +5676,14 @@
         </is>
       </c>
       <c r="N41" s="6" t="n">
-        <v>-0.006584844855287264</v>
+        <v>-0.009704674687064652</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
         <v>16</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>0.05858151479569788</v>
+        <v>0.05746773346165605</v>
       </c>
     </row>
     <row r="42">
@@ -5911,25 +6047,25 @@
         <v>0.2970374560127521</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.3238511610240272</v>
+        <v>0.3056843702034556</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Tipico</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.02681370501127511</v>
+        <v>-0.008646914190703514</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
         <v>18</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>0.06939602747460528</v>
+        <v>0.06949609497402987</v>
       </c>
     </row>
     <row r="48">
@@ -5974,92 +6110,88 @@
         <v>0.2460926947406865</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.2741254230990199</v>
+        <v>0.2717412733681283</v>
       </c>
       <c r="L48" s="5" t="n">
         <v>3.6</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>Winamax (DE)</t>
         </is>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.02803272835833334</v>
+        <v>-0.02564857862744177</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
         <v>18</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>0.06939602747460528</v>
+        <v>0.06949609497402987</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Italy Serie A</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>sassuolo v lazio</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="5" t="n">
         <v>1.12</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F49" t="n">
         <v>5</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G49" t="n">
         <v>13</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Away (2)</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n">
+      <c r="J49" s="6" t="n">
         <v>0.4568698492465614</v>
       </c>
-      <c r="K49" s="4" t="n">
-        <v>0.4020234158769529</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>GTbets</t>
-        </is>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v>0.05484643336960848</v>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="n">
+      <c r="K49" s="6" t="n">
+        <v>0.4225743564284161</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Unibet (SE)</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>0.03429549281814531</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
         <v>18</v>
       </c>
-      <c r="Q49" s="4" t="n">
-        <v>0.06939602747460528</v>
+      <c r="Q49" s="6" t="n">
+        <v>0.06949609497402987</v>
       </c>
     </row>
     <row r="50">
@@ -6104,10 +6236,10 @@
         <v>0.4873380195195516</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.5490983406595378</v>
+        <v>0.5511816056677418</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -6115,14 +6247,14 @@
         </is>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.06176032113998614</v>
+        <v>-0.06384358614819013</v>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
         <v>12</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>0.06210541739120242</v>
+        <v>0.06173154939653269</v>
       </c>
     </row>
     <row r="51">
@@ -6167,18 +6299,18 @@
         <v>0.5126619804804484</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0.4509016593404622</v>
+        <v>0.4488183943322583</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Tipico</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.0617603211399862</v>
+        <v>0.06384358614819013</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -6189,7 +6321,7 @@
         <v>12</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>0.06210541739120242</v>
+        <v>0.06173154939653269</v>
       </c>
     </row>
     <row r="52">
@@ -7191,10 +7323,10 @@
         <v>0.1686838437270223</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>0.1517424439739041</v>
+        <v>0.178642734132465</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -7202,14 +7334,14 @@
         </is>
       </c>
       <c r="N67" s="6" t="n">
-        <v>0.01694139975311823</v>
+        <v>-0.009958890405442622</v>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
         <v>20</v>
       </c>
       <c r="Q67" s="6" t="n">
-        <v>0.06290640724104739</v>
+        <v>0.06290794719758377</v>
       </c>
     </row>
     <row r="68">
@@ -7254,151 +7386,159 @@
         <v>0.1482581727874156</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>0.177514399055003</v>
+        <v>0.1903057205547849</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>5.75</v>
+        <v>5.28</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>-0.02925622626758745</v>
+        <v>-0.04204754776736933</v>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
         <v>20</v>
       </c>
       <c r="Q68" s="6" t="n">
-        <v>0.06290640724104739</v>
+        <v>0.06290794719758377</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Germany Bundesliga</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>freiburg v bayern munich</t>
         </is>
       </c>
-      <c r="D69" s="5" t="n">
+      <c r="D69" s="3" t="n">
         <v>1.34</v>
       </c>
-      <c r="E69" s="5" t="n">
+      <c r="E69" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>Away (2)</t>
         </is>
       </c>
-      <c r="J69" s="6" t="n">
+      <c r="J69" s="4" t="n">
         <v>0.6830579834855618</v>
       </c>
-      <c r="K69" s="6" t="n">
-        <v>0.6707431569710929</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>1xBet</t>
-        </is>
-      </c>
-      <c r="N69" s="6" t="n">
-        <v>0.01231482651446891</v>
-      </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="n">
+      <c r="K69" s="4" t="n">
+        <v>0.6310515453127501</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>Codere (IT)</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="n">
+        <v>0.0520064381728117</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="Q69" s="6" t="n">
-        <v>0.06290640724104739</v>
+      <c r="Q69" s="4" t="n">
+        <v>0.06290794719758377</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Germany Bundesliga</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>freiburg v bayern munich</t>
         </is>
       </c>
-      <c r="D70" s="5" t="n">
+      <c r="D70" s="3" t="n">
         <v>1.34</v>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E70" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Over/Under 2.5 goals</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>Over</t>
         </is>
       </c>
-      <c r="J70" s="6" t="n">
+      <c r="J70" s="4" t="n">
         <v>0.78087790448716</v>
       </c>
-      <c r="K70" s="6" t="n">
-        <v>0.7315674065940985</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>William Hill</t>
-        </is>
-      </c>
-      <c r="N70" s="6" t="n">
-        <v>0.04931049789306152</v>
-      </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="n">
+      <c r="K70" s="4" t="n">
+        <v>0.7228476869170627</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Betsson</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>0.0580302175700973</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q70" s="6" t="n">
-        <v>0.05700047334311479</v>
+      <c r="Q70" s="4" t="n">
+        <v>0.05608522400463204</v>
       </c>
     </row>
     <row r="71">
@@ -7443,10 +7583,10 @@
         <v>0.21912209551284</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>0.2684325934059015</v>
+        <v>0.2771523130829373</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -7454,14 +7594,14 @@
         </is>
       </c>
       <c r="N71" s="6" t="n">
-        <v>-0.04931049789306147</v>
+        <v>-0.05803021757009724</v>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
         <v>3</v>
       </c>
       <c r="Q71" s="6" t="n">
-        <v>0.05700047334311479</v>
+        <v>0.05608522400463204</v>
       </c>
     </row>
     <row r="72">
@@ -7506,25 +7646,25 @@
         <v>0.3136926592262153</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>0.3218644041427529</v>
+        <v>0.3149397442783014</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Tipico</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N72" s="6" t="n">
-        <v>-0.00817174491653766</v>
+        <v>-0.00124708505208615</v>
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
         <v>20</v>
       </c>
       <c r="Q72" s="6" t="n">
-        <v>0.06352402661157328</v>
+        <v>0.06403130198470125</v>
       </c>
     </row>
     <row r="73">
@@ -7569,10 +7709,10 @@
         <v>0.2047922115626695</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>0.2352942709375348</v>
+        <v>0.2338669435183827</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -7580,14 +7720,14 @@
         </is>
       </c>
       <c r="N73" s="6" t="n">
-        <v>-0.0305020593748653</v>
+        <v>-0.02907473195571314</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
         <v>20</v>
       </c>
       <c r="Q73" s="6" t="n">
-        <v>0.06352402661157328</v>
+        <v>0.06403130198470125</v>
       </c>
     </row>
     <row r="74">
@@ -7632,10 +7772,10 @@
         <v>0.4815151292111152</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>0.4428413249197122</v>
+        <v>0.4511933122033159</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -7643,14 +7783,14 @@
         </is>
       </c>
       <c r="N74" s="6" t="n">
-        <v>0.03867380429140305</v>
+        <v>0.03032181700779929</v>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="n">
         <v>20</v>
       </c>
       <c r="Q74" s="6" t="n">
-        <v>0.06352402661157328</v>
+        <v>0.06403130198470125</v>
       </c>
     </row>
     <row r="75">
@@ -7695,10 +7835,10 @@
         <v>0.7473110835112107</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>0.7239742871521218</v>
+        <v>0.7192648039537574</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -7706,14 +7846,14 @@
         </is>
       </c>
       <c r="N75" s="6" t="n">
-        <v>0.02333679635908892</v>
+        <v>0.02804627955745331</v>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="n">
         <v>3</v>
       </c>
       <c r="Q75" s="6" t="n">
-        <v>0.05986865916061612</v>
+        <v>0.06136691065602151</v>
       </c>
     </row>
     <row r="76">
@@ -7758,10 +7898,10 @@
         <v>0.2526889164887893</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>0.2760257128478783</v>
+        <v>0.2807351960462427</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -7769,14 +7909,14 @@
         </is>
       </c>
       <c r="N76" s="6" t="n">
-        <v>-0.02333679635908897</v>
+        <v>-0.02804627955745337</v>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
         <v>3</v>
       </c>
       <c r="Q76" s="6" t="n">
-        <v>0.05986865916061612</v>
+        <v>0.06136691065602151</v>
       </c>
     </row>
     <row r="77">
@@ -7821,25 +7961,25 @@
         <v>0.2555376289891718</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>0.3203716802114202</v>
+        <v>0.3166828675177488</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N77" s="6" t="n">
-        <v>-0.06483405122224839</v>
+        <v>-0.06114523852857706</v>
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q77" s="6" t="n">
-        <v>0.05924797246680177</v>
+        <v>0.05914580618685607</v>
       </c>
     </row>
     <row r="78">
@@ -7884,7 +8024,7 @@
         <v>0.259790805440283</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>0.2885707956769117</v>
+        <v>0.2902602552622457</v>
       </c>
       <c r="L78" s="5" t="n">
         <v>3.4</v>
@@ -7895,14 +8035,14 @@
         </is>
       </c>
       <c r="N78" s="6" t="n">
-        <v>-0.02877999023662864</v>
+        <v>-0.03046944982196265</v>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q78" s="6" t="n">
-        <v>0.05924797246680177</v>
+        <v>0.05914580618685607</v>
       </c>
     </row>
     <row r="79">
@@ -7947,7 +8087,7 @@
         <v>0.4846715655705451</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0.3910575241116682</v>
+        <v>0.3930568772200054</v>
       </c>
       <c r="L79" s="3" t="n">
         <v>2.52</v>
@@ -7958,7 +8098,7 @@
         </is>
       </c>
       <c r="N79" s="4" t="n">
-        <v>0.09361404145887692</v>
+        <v>0.09161468835053965</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -7966,10 +8106,10 @@
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>0.05924797246680177</v>
+        <v>0.05914580618685607</v>
       </c>
     </row>
     <row r="80">
@@ -8014,7 +8154,7 @@
         <v>0.3898027635304929</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>0.4703389319449311</v>
+        <v>0.4705330313238131</v>
       </c>
       <c r="L80" s="5" t="n">
         <v>2.08</v>
@@ -8025,14 +8165,14 @@
         </is>
       </c>
       <c r="N80" s="6" t="n">
-        <v>-0.08053616841443823</v>
+        <v>-0.08073026779332021</v>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="n">
         <v>14</v>
       </c>
       <c r="Q80" s="6" t="n">
-        <v>0.06139247446267226</v>
+        <v>0.06134866912342542</v>
       </c>
     </row>
     <row r="81">
@@ -8077,7 +8217,7 @@
         <v>0.6101972364695072</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0.5296610680550689</v>
+        <v>0.5294669686761869</v>
       </c>
       <c r="L81" s="3" t="n">
         <v>1.87</v>
@@ -8088,7 +8228,7 @@
         </is>
       </c>
       <c r="N81" s="4" t="n">
-        <v>0.08053616841443834</v>
+        <v>0.08073026779332027</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -8099,74 +8239,70 @@
         <v>14</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>0.06139247446267226</v>
+        <v>0.06134866912342542</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>France Ligue 1</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>marseille v le havre</t>
         </is>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="D82" s="5" t="n">
         <v>2.09</v>
       </c>
-      <c r="E82" s="3" t="n">
+      <c r="E82" s="5" t="n">
         <v>0.83</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F82" t="n">
         <v>6</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="G82" t="n">
         <v>1</v>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>Home (1)</t>
         </is>
       </c>
-      <c r="J82" s="4" t="n">
+      <c r="J82" s="6" t="n">
         <v>0.680156878514566</v>
       </c>
-      <c r="K82" s="4" t="n">
-        <v>0.6290135236880946</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>1xBet</t>
-        </is>
-      </c>
-      <c r="N82" s="4" t="n">
-        <v>0.05114335482647137</v>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P82" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q82" s="4" t="n">
-        <v>0.05900876966252728</v>
+      <c r="K82" s="6" t="n">
+        <v>0.637786513180526</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>GTbets</t>
+        </is>
+      </c>
+      <c r="N82" s="6" t="n">
+        <v>0.04237036533403993</v>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q82" s="6" t="n">
+        <v>0.06241635769813357</v>
       </c>
     </row>
     <row r="83">
@@ -8211,25 +8347,25 @@
         <v>0.1750458894048774</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>0.1991035731730888</v>
+        <v>0.1967129696478342</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>5.02</v>
+        <v>5.08</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N83" s="6" t="n">
-        <v>-0.02405768376821138</v>
+        <v>-0.02166708024295674</v>
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q83" s="6" t="n">
-        <v>0.05900876966252728</v>
+        <v>0.06241635769813357</v>
       </c>
     </row>
     <row r="84">
@@ -8274,25 +8410,25 @@
         <v>0.1447972320805564</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>0.1718829031388165</v>
+        <v>0.1655005171716398</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>LeoVegas (SE)</t>
+          <t>Tipico</t>
         </is>
       </c>
       <c r="N84" s="6" t="n">
-        <v>-0.02708567105826007</v>
+        <v>-0.02070328509108332</v>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q84" s="6" t="n">
-        <v>0.05900876966252728</v>
+        <v>0.06241635769813357</v>
       </c>
     </row>
     <row r="85">
@@ -8467,7 +8603,7 @@
         <v>0.4084387731517211</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>0.4794445866941817</v>
+        <v>0.4834804937215577</v>
       </c>
       <c r="L87" s="5" t="n">
         <v>2.06</v>
@@ -8478,14 +8614,14 @@
         </is>
       </c>
       <c r="N87" s="6" t="n">
-        <v>-0.07100581354246061</v>
+        <v>-0.07504172056983666</v>
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q87" s="6" t="n">
-        <v>0.06130533099238902</v>
+        <v>0.06197068707280271</v>
       </c>
     </row>
     <row r="88">
@@ -8530,10 +8666,10 @@
         <v>0.2656534478344337</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>0.2750235032772096</v>
+        <v>0.272428632755734</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -8541,14 +8677,14 @@
         </is>
       </c>
       <c r="N88" s="6" t="n">
-        <v>-0.009370055442775915</v>
+        <v>-0.006775184921300359</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q88" s="6" t="n">
-        <v>0.06130533099238902</v>
+        <v>0.06197068707280271</v>
       </c>
     </row>
     <row r="89">
@@ -8593,7 +8729,7 @@
         <v>0.3259077790138454</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0.2455319100286087</v>
+        <v>0.2440908735227083</v>
       </c>
       <c r="L89" s="3" t="n">
         <v>4.25</v>
@@ -8604,7 +8740,7 @@
         </is>
       </c>
       <c r="N89" s="4" t="n">
-        <v>0.08037586898523666</v>
+        <v>0.08181690549113713</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -8612,10 +8748,10 @@
         </is>
       </c>
       <c r="P89" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>0.06130533099238902</v>
+        <v>0.06197068707280271</v>
       </c>
     </row>
     <row r="90">
@@ -8660,7 +8796,7 @@
         <v>0.4167614283267509</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>0.5254502576085637</v>
+        <v>0.5250191910905406</v>
       </c>
       <c r="L90" s="5" t="n">
         <v>1.88</v>
@@ -8671,14 +8807,14 @@
         </is>
       </c>
       <c r="N90" s="6" t="n">
-        <v>-0.1086888292818127</v>
+        <v>-0.1082577627637897</v>
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
         <v>15</v>
       </c>
       <c r="Q90" s="6" t="n">
-        <v>0.05719057656487729</v>
+        <v>0.05692659540799021</v>
       </c>
     </row>
     <row r="91">
@@ -8723,7 +8859,7 @@
         <v>0.5832385716732491</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0.4745497423914363</v>
+        <v>0.4749808089094593</v>
       </c>
       <c r="L91" s="3" t="n">
         <v>2.08</v>
@@ -8734,7 +8870,7 @@
         </is>
       </c>
       <c r="N91" s="4" t="n">
-        <v>0.1086888292818128</v>
+        <v>0.1082577627637898</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -8745,7 +8881,7 @@
         <v>15</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>0.05719057656487729</v>
+        <v>0.05692659540799021</v>
       </c>
     </row>
     <row r="92">
@@ -8790,7 +8926,7 @@
         <v>0.5068466783874341</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>0.5330878743298315</v>
+        <v>0.5342206783830663</v>
       </c>
       <c r="L92" s="5" t="n">
         <v>1.83</v>
@@ -8801,14 +8937,14 @@
         </is>
       </c>
       <c r="N92" s="6" t="n">
-        <v>-0.02624119594239738</v>
+        <v>-0.02737399999563217</v>
       </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q92" s="6" t="n">
-        <v>0.06254524023914335</v>
+        <v>0.06252337709105346</v>
       </c>
     </row>
     <row r="93">
@@ -8853,7 +8989,7 @@
         <v>0.193773477326576</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>0.2247931531469321</v>
+        <v>0.2258525042788368</v>
       </c>
       <c r="L93" s="5" t="n">
         <v>4.4</v>
@@ -8864,14 +9000,14 @@
         </is>
       </c>
       <c r="N93" s="6" t="n">
-        <v>-0.03101967582035614</v>
+        <v>-0.03207902695226081</v>
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q93" s="6" t="n">
-        <v>0.06254524023914335</v>
+        <v>0.06252337709105346</v>
       </c>
     </row>
     <row r="94">
@@ -8916,7 +9052,7 @@
         <v>0.2993798442859898</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0.2421189725232363</v>
+        <v>0.239926817338097</v>
       </c>
       <c r="L94" s="3" t="n">
         <v>4.21</v>
@@ -8927,7 +9063,7 @@
         </is>
       </c>
       <c r="N94" s="4" t="n">
-        <v>0.05726087176275352</v>
+        <v>0.05945302694789284</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -8935,10 +9071,10 @@
         </is>
       </c>
       <c r="P94" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q94" s="4" t="n">
-        <v>0.06254524023914335</v>
+        <v>0.06252337709105346</v>
       </c>
     </row>
     <row r="95">
@@ -8983,18 +9119,18 @@
         <v>0.7775009235052397</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0.6584233068844428</v>
+        <v>0.6555057877689695</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>William Hill</t>
+          <t>Betsson</t>
         </is>
       </c>
       <c r="N95" s="4" t="n">
-        <v>0.1190776166207969</v>
+        <v>0.1219951357362702</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -9005,7 +9141,7 @@
         <v>3</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>0.05720969307838334</v>
+        <v>0.05699124479250547</v>
       </c>
     </row>
     <row r="96">
@@ -9050,10 +9186,10 @@
         <v>0.2224990764947603</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>0.3415766931155571</v>
+        <v>0.3444942122310304</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -9061,14 +9197,14 @@
         </is>
       </c>
       <c r="N96" s="6" t="n">
-        <v>-0.1190776166207967</v>
+        <v>-0.1219951357362701</v>
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="n">
         <v>3</v>
       </c>
       <c r="Q96" s="6" t="n">
-        <v>0.05720969307838334</v>
+        <v>0.05699124479250547</v>
       </c>
     </row>
     <row r="97">
@@ -9113,7 +9249,7 @@
         <v>0.4978156477707739</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>0.6679413360761134</v>
+        <v>0.6763078389502943</v>
       </c>
       <c r="L97" s="5" t="n">
         <v>1.46</v>
@@ -9124,77 +9260,81 @@
         </is>
       </c>
       <c r="N97" s="6" t="n">
-        <v>-0.1701256883053395</v>
+        <v>-0.1784921911795204</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q97" s="6" t="n">
-        <v>0.06181908972904252</v>
+        <v>0.05920154042564959</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>France Ligue 1</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>paris saint germain v lyon</t>
         </is>
       </c>
-      <c r="D98" s="5" t="n">
+      <c r="D98" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="E98" s="5" t="n">
+      <c r="E98" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="G98" t="n">
+      <c r="G98" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>Draw (X)</t>
         </is>
       </c>
-      <c r="J98" s="6" t="n">
+      <c r="J98" s="4" t="n">
         <v>0.2289518790465764</v>
       </c>
-      <c r="K98" s="6" t="n">
-        <v>0.1814518229052236</v>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>BetOnline.ag</t>
-        </is>
-      </c>
-      <c r="N98" s="6" t="n">
-        <v>0.04750005614135275</v>
-      </c>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q98" s="6" t="n">
-        <v>0.06181908972904252</v>
+      <c r="K98" s="4" t="n">
+        <v>0.1783666016591509</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="n">
+        <v>0.05058527738742552</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q98" s="4" t="n">
+        <v>0.05920154042564959</v>
       </c>
     </row>
     <row r="99">
@@ -9239,18 +9379,18 @@
         <v>0.2732324731826497</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0.1506068410186629</v>
+        <v>0.1453255593905549</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>BetOnline.ag</t>
+          <t>Nordic Bet</t>
         </is>
       </c>
       <c r="N99" s="4" t="n">
-        <v>0.1226256321639868</v>
+        <v>0.1279069137920948</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -9258,10 +9398,10 @@
         </is>
       </c>
       <c r="P99" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>0.06181908972904252</v>
+        <v>0.05920154042564959</v>
       </c>
     </row>
     <row r="100">
@@ -9306,10 +9446,10 @@
         <v>0.518258375435965</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>0.6885648281221721</v>
+        <v>0.6851969455730161</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -9317,14 +9457,14 @@
         </is>
       </c>
       <c r="N100" s="6" t="n">
-        <v>-0.1703064526862071</v>
+        <v>-0.1669385701370512</v>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="n">
         <v>3</v>
       </c>
       <c r="Q100" s="6" t="n">
-        <v>0.06281172521075711</v>
+        <v>0.06284646798033822</v>
       </c>
     </row>
     <row r="101">
@@ -9369,10 +9509,10 @@
         <v>0.481741624564035</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0.3114351718778278</v>
+        <v>0.3148030544269839</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -9380,7 +9520,7 @@
         </is>
       </c>
       <c r="N101" s="4" t="n">
-        <v>0.1703064526862072</v>
+        <v>0.1669385701370511</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -9391,70 +9531,74 @@
         <v>3</v>
       </c>
       <c r="Q101" s="4" t="n">
-        <v>0.06281172521075711</v>
+        <v>0.06284646798033822</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Netherlands Eredivisie</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>for sittard v excelsior</t>
         </is>
       </c>
-      <c r="D102" s="5" t="n">
+      <c r="D102" s="3" t="n">
         <v>1.68</v>
       </c>
-      <c r="E102" s="5" t="n">
+      <c r="E102" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G102" t="n">
+      <c r="G102" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>Home (1)</t>
         </is>
       </c>
-      <c r="J102" s="6" t="n">
+      <c r="J102" s="4" t="n">
         <v>0.4156544274247579</v>
       </c>
-      <c r="K102" s="6" t="n">
-        <v>0.3977659679057415</v>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="M102" t="inlineStr">
+      <c r="K102" s="4" t="n">
+        <v>0.3595033492136283</v>
+      </c>
+      <c r="L102" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
         <is>
           <t>Pinnacle</t>
         </is>
       </c>
-      <c r="N102" s="6" t="n">
-        <v>0.01788845951901646</v>
-      </c>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="n">
+      <c r="N102" s="4" t="n">
+        <v>0.05615107821112969</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="Q102" s="6" t="n">
-        <v>0.07795946880690849</v>
+      <c r="Q102" s="4" t="n">
+        <v>0.07791338810172883</v>
       </c>
     </row>
     <row r="103">
@@ -9499,25 +9643,25 @@
         <v>0.2509650941050725</v>
       </c>
       <c r="K103" s="6" t="n">
-        <v>0.267967267857919</v>
+        <v>0.2710572034481583</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N103" s="6" t="n">
-        <v>-0.01700217375284652</v>
+        <v>-0.02009210934308586</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
         <v>20</v>
       </c>
       <c r="Q103" s="6" t="n">
-        <v>0.07795946880690849</v>
+        <v>0.07791338810172883</v>
       </c>
     </row>
     <row r="104">
@@ -9562,10 +9706,10 @@
         <v>0.3333804784701697</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>0.3342667642363396</v>
+        <v>0.3694394473382135</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -9573,14 +9717,14 @@
         </is>
       </c>
       <c r="N104" s="6" t="n">
-        <v>-0.000886285766169892</v>
+        <v>-0.03605896886804388</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="n">
         <v>20</v>
       </c>
       <c r="Q104" s="6" t="n">
-        <v>0.07795946880690849</v>
+        <v>0.07791338810172883</v>
       </c>
     </row>
     <row r="105">
@@ -9625,10 +9769,10 @@
         <v>0.6213574486486763</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0.5664536154159017</v>
+        <v>0.5564864909435647</v>
       </c>
       <c r="L105" s="3" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -9636,7 +9780,7 @@
         </is>
       </c>
       <c r="N105" s="4" t="n">
-        <v>0.05490383323277459</v>
+        <v>0.06487095770511153</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -9644,10 +9788,10 @@
         </is>
       </c>
       <c r="P105" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q105" s="4" t="n">
-        <v>0.07524549285010108</v>
+        <v>0.07273612235029109</v>
       </c>
     </row>
     <row r="106">
@@ -9692,10 +9836,10 @@
         <v>0.3786425513513237</v>
       </c>
       <c r="K106" s="6" t="n">
-        <v>0.4335463845840984</v>
+        <v>0.4435135090564354</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -9703,14 +9847,14 @@
         </is>
       </c>
       <c r="N106" s="6" t="n">
-        <v>-0.05490383323277465</v>
+        <v>-0.06487095770511164</v>
       </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q106" s="6" t="n">
-        <v>0.07524549285010108</v>
+        <v>0.07273612235029109</v>
       </c>
     </row>
     <row r="107">
@@ -9755,10 +9899,10 @@
         <v>0.4495442318657261</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>0.4219692062333091</v>
+        <v>0.4256692786904139</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -9766,14 +9910,14 @@
         </is>
       </c>
       <c r="N107" s="6" t="n">
-        <v>0.02757502563241698</v>
+        <v>0.02387495317531213</v>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="n">
         <v>20</v>
       </c>
       <c r="Q107" s="6" t="n">
-        <v>0.07764494220865277</v>
+        <v>0.0769673602756379</v>
       </c>
     </row>
     <row r="108">
@@ -9818,7 +9962,7 @@
         <v>0.2333644470986393</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>0.2466807759399686</v>
+        <v>0.2466827089220463</v>
       </c>
       <c r="L108" s="5" t="n">
         <v>4</v>
@@ -9829,14 +9973,14 @@
         </is>
       </c>
       <c r="N108" s="6" t="n">
-        <v>-0.01331632884132933</v>
+        <v>-0.01331826182340703</v>
       </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="n">
         <v>20</v>
       </c>
       <c r="Q108" s="6" t="n">
-        <v>0.07764494220865277</v>
+        <v>0.0769673602756379</v>
       </c>
     </row>
     <row r="109">
@@ -9881,25 +10025,25 @@
         <v>0.3170913210356348</v>
       </c>
       <c r="K109" s="6" t="n">
-        <v>0.3313500178267223</v>
+        <v>0.3276480123875398</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Unibet (NL)</t>
         </is>
       </c>
       <c r="N109" s="6" t="n">
-        <v>-0.01425869679108754</v>
+        <v>-0.01055669135190501</v>
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="n">
         <v>20</v>
       </c>
       <c r="Q109" s="6" t="n">
-        <v>0.07764494220865277</v>
+        <v>0.0769673602756379</v>
       </c>
     </row>
     <row r="110">
@@ -10070,25 +10214,25 @@
         <v>0.4469518662096583</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>0.4930720039591047</v>
+        <v>0.5273437426309731</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>GTbets</t>
         </is>
       </c>
       <c r="N112" s="6" t="n">
-        <v>-0.04612013774944634</v>
+        <v>-0.08039187642131473</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="n">
         <v>18</v>
       </c>
       <c r="Q112" s="6" t="n">
-        <v>0.08749488795580214</v>
+        <v>0.08905558001285976</v>
       </c>
     </row>
     <row r="113">
@@ -10133,25 +10277,25 @@
         <v>0.2446441608652773</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>0.2635558896915937</v>
+        <v>0.2553252057389692</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>GTbets</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N113" s="6" t="n">
-        <v>-0.01891172882631639</v>
+        <v>-0.01068104487369184</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
         <v>18</v>
       </c>
       <c r="Q113" s="6" t="n">
-        <v>0.08749488795580214</v>
+        <v>0.08905558001285976</v>
       </c>
     </row>
     <row r="114">
@@ -10196,18 +10340,18 @@
         <v>0.3084039729250643</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0.2433721063493016</v>
+        <v>0.2173310516300578</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>4</v>
+        <v>4.74</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Tipico</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N114" s="4" t="n">
-        <v>0.06503186657576271</v>
+        <v>0.09107292129500652</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -10218,7 +10362,7 @@
         <v>18</v>
       </c>
       <c r="Q114" s="4" t="n">
-        <v>0.08749488795580214</v>
+        <v>0.08905558001285976</v>
       </c>
     </row>
     <row r="115">
@@ -10263,10 +10407,10 @@
         <v>0.4852846405442422</v>
       </c>
       <c r="K115" s="6" t="n">
-        <v>0.5021496743097958</v>
+        <v>0.5055240467294332</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -10274,14 +10418,14 @@
         </is>
       </c>
       <c r="N115" s="6" t="n">
-        <v>-0.01686503376555365</v>
+        <v>-0.02023940618519099</v>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="n">
         <v>13</v>
       </c>
       <c r="Q115" s="6" t="n">
-        <v>0.07564724552035175</v>
+        <v>0.07449646870799974</v>
       </c>
     </row>
     <row r="116">
@@ -10326,10 +10470,10 @@
         <v>0.5147153594557579</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>0.4978503256902042</v>
+        <v>0.4944759532705669</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -10337,14 +10481,14 @@
         </is>
       </c>
       <c r="N116" s="6" t="n">
-        <v>0.01686503376555365</v>
+        <v>0.02023940618519099</v>
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="n">
         <v>13</v>
       </c>
       <c r="Q116" s="6" t="n">
-        <v>0.07564724552035175</v>
+        <v>0.07449646870799974</v>
       </c>
     </row>
     <row r="117">
@@ -10389,18 +10533,18 @@
         <v>0.216953187415267</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0.160243976202629</v>
+        <v>0.1521324132946012</v>
       </c>
       <c r="L117" s="3" t="n">
-        <v>6.25</v>
+        <v>6.83</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N117" s="4" t="n">
-        <v>0.05670921121263806</v>
+        <v>0.06482077412066584</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -10411,7 +10555,7 @@
         <v>18</v>
       </c>
       <c r="Q117" s="4" t="n">
-        <v>0.09030960307884524</v>
+        <v>0.09089332170160785</v>
       </c>
     </row>
     <row r="118">
@@ -10456,10 +10600,10 @@
         <v>0.2035206094614778</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>0.2319059993790525</v>
+        <v>0.2264811128519244</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>4.35</v>
+        <v>4.42</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -10467,14 +10611,14 @@
         </is>
       </c>
       <c r="N118" s="6" t="n">
-        <v>-0.02838538991757461</v>
+        <v>-0.02296050339044656</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
         <v>18</v>
       </c>
       <c r="Q118" s="6" t="n">
-        <v>0.09030960307884524</v>
+        <v>0.09089332170160785</v>
       </c>
     </row>
     <row r="119">
@@ -10519,10 +10663,10 @@
         <v>0.579526203123255</v>
       </c>
       <c r="K119" s="6" t="n">
-        <v>0.6078500244183185</v>
+        <v>0.6213864738534745</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -10530,14 +10674,14 @@
         </is>
       </c>
       <c r="N119" s="6" t="n">
-        <v>-0.0283238212950635</v>
+        <v>-0.04186027073021947</v>
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="n">
         <v>18</v>
       </c>
       <c r="Q119" s="6" t="n">
-        <v>0.09030960307884524</v>
+        <v>0.09089332170160785</v>
       </c>
     </row>
     <row r="120">
@@ -10582,10 +10726,10 @@
         <v>0.5323982265428717</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>0.512057359741291</v>
+        <v>0.5088012560656254</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -10593,14 +10737,14 @@
         </is>
       </c>
       <c r="N120" s="6" t="n">
-        <v>0.02034086680158076</v>
+        <v>0.02359697047724629</v>
       </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="n">
         <v>13</v>
       </c>
       <c r="Q120" s="6" t="n">
-        <v>0.07541465112994805</v>
+        <v>0.07513291788447508</v>
       </c>
     </row>
     <row r="121">
@@ -10645,10 +10789,10 @@
         <v>0.4676017734571283</v>
       </c>
       <c r="K121" s="6" t="n">
-        <v>0.4879426402587089</v>
+        <v>0.4911987439343747</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -10656,14 +10800,14 @@
         </is>
       </c>
       <c r="N121" s="6" t="n">
-        <v>-0.02034086680158065</v>
+        <v>-0.0235969704772464</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
         <v>13</v>
       </c>
       <c r="Q121" s="6" t="n">
-        <v>0.07541465112994805</v>
+        <v>0.07513291788447508</v>
       </c>
     </row>
     <row r="122">
@@ -10708,7 +10852,7 @@
         <v>0.7520420956786665</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0.6969049692474001</v>
+        <v>0.6996566542313409</v>
       </c>
       <c r="L122" s="3" t="n">
         <v>1.36</v>
@@ -10719,7 +10863,7 @@
         </is>
       </c>
       <c r="N122" s="4" t="n">
-        <v>0.05513712643126645</v>
+        <v>0.0523854414473256</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -10730,7 +10874,7 @@
         <v>19</v>
       </c>
       <c r="Q122" s="4" t="n">
-        <v>0.08731577481307091</v>
+        <v>0.08553870890063733</v>
       </c>
     </row>
     <row r="123">
@@ -10775,10 +10919,10 @@
         <v>0.1332472213290279</v>
       </c>
       <c r="K123" s="6" t="n">
-        <v>0.1674016181890106</v>
+        <v>0.1654531748586766</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>6.04</v>
+        <v>6.16</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -10786,14 +10930,14 @@
         </is>
       </c>
       <c r="N123" s="6" t="n">
-        <v>-0.0341543968599827</v>
+        <v>-0.03220595352964867</v>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="n">
         <v>19</v>
       </c>
       <c r="Q123" s="6" t="n">
-        <v>0.08731577481307091</v>
+        <v>0.08553870890063733</v>
       </c>
     </row>
     <row r="124">
@@ -10838,25 +10982,25 @@
         <v>0.1147106829923054</v>
       </c>
       <c r="K124" s="6" t="n">
-        <v>0.1356934125635893</v>
+        <v>0.1348901709099825</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>7.5</v>
+        <v>7.54</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N124" s="6" t="n">
-        <v>-0.02098272957128386</v>
+        <v>-0.02017948791767704</v>
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="n">
         <v>19</v>
       </c>
       <c r="Q124" s="6" t="n">
-        <v>0.08731577481307091</v>
+        <v>0.08553870890063733</v>
       </c>
     </row>
     <row r="125">
@@ -10901,25 +11045,25 @@
         <v>0.5194831218757243</v>
       </c>
       <c r="K125" s="6" t="n">
-        <v>0.5384506402174947</v>
+        <v>0.5393707837115912</v>
       </c>
       <c r="L125" s="5" t="n">
         <v>1.77</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N125" s="6" t="n">
-        <v>-0.01896751834177035</v>
+        <v>-0.01988766183586688</v>
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="n">
         <v>19</v>
       </c>
       <c r="Q125" s="6" t="n">
-        <v>0.0869403260062359</v>
+        <v>0.08704740964075315</v>
       </c>
     </row>
     <row r="126">
@@ -10964,7 +11108,7 @@
         <v>0.2384030960670402</v>
       </c>
       <c r="K126" s="6" t="n">
-        <v>0.2478107622291419</v>
+        <v>0.2486745999374512</v>
       </c>
       <c r="L126" s="5" t="n">
         <v>4</v>
@@ -10975,14 +11119,14 @@
         </is>
       </c>
       <c r="N126" s="6" t="n">
-        <v>-0.009407666162101674</v>
+        <v>-0.01027150387041101</v>
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="n">
         <v>19</v>
       </c>
       <c r="Q126" s="6" t="n">
-        <v>0.0869403260062359</v>
+        <v>0.08704740964075315</v>
       </c>
     </row>
     <row r="127">
@@ -11027,10 +11171,10 @@
         <v>0.2421137820572355</v>
       </c>
       <c r="K127" s="6" t="n">
-        <v>0.2137385975533634</v>
+        <v>0.2119546163509576</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -11038,14 +11182,14 @@
         </is>
       </c>
       <c r="N127" s="6" t="n">
-        <v>0.02837518450387205</v>
+        <v>0.03015916570627786</v>
       </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="n">
         <v>19</v>
       </c>
       <c r="Q127" s="6" t="n">
-        <v>0.0869403260062359</v>
+        <v>0.08704740964075315</v>
       </c>
     </row>
     <row r="128">
@@ -11090,10 +11234,10 @@
         <v>0.4658645760359786</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0.4053182123611488</v>
+        <v>0.4102233486507934</v>
       </c>
       <c r="L128" s="3" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
@@ -11101,7 +11245,7 @@
         </is>
       </c>
       <c r="N128" s="4" t="n">
-        <v>0.0605463636748298</v>
+        <v>0.05564122738518529</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -11112,7 +11256,7 @@
         <v>19</v>
       </c>
       <c r="Q128" s="4" t="n">
-        <v>0.08972443165966462</v>
+        <v>0.09024113188408286</v>
       </c>
     </row>
     <row r="129">
@@ -11157,7 +11301,7 @@
         <v>0.2563716628832448</v>
       </c>
       <c r="K129" s="6" t="n">
-        <v>0.2944156169536792</v>
+        <v>0.2941738949789715</v>
       </c>
       <c r="L129" s="5" t="n">
         <v>3.3</v>
@@ -11168,14 +11312,14 @@
         </is>
       </c>
       <c r="N129" s="6" t="n">
-        <v>-0.03804395407043448</v>
+        <v>-0.0378022320957267</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="n">
         <v>19</v>
       </c>
       <c r="Q129" s="6" t="n">
-        <v>0.08972443165966462</v>
+        <v>0.09024113188408286</v>
       </c>
     </row>
     <row r="130">
@@ -11220,7 +11364,7 @@
         <v>0.2777637610807767</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>0.3002661706851719</v>
+        <v>0.2956027563702353</v>
       </c>
       <c r="L130" s="5" t="n">
         <v>3.36</v>
@@ -11231,14 +11375,14 @@
         </is>
       </c>
       <c r="N130" s="6" t="n">
-        <v>-0.0225024096043952</v>
+        <v>-0.01783899528945854</v>
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="n">
         <v>19</v>
       </c>
       <c r="Q130" s="6" t="n">
-        <v>0.08972443165966462</v>
+        <v>0.09024113188408286</v>
       </c>
     </row>
     <row r="131">
@@ -11472,7 +11616,7 @@
         <v>0.418045873071459</v>
       </c>
       <c r="K134" s="6" t="n">
-        <v>0.4669248128660126</v>
+        <v>0.4670322623452702</v>
       </c>
       <c r="L134" s="5" t="n">
         <v>2.05</v>
@@ -11483,14 +11627,14 @@
         </is>
       </c>
       <c r="N134" s="6" t="n">
-        <v>-0.04887893979455354</v>
+        <v>-0.04898638927381116</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="n">
         <v>15</v>
       </c>
       <c r="Q134" s="6" t="n">
-        <v>0.09071098079944635</v>
+        <v>0.09082830515486726</v>
       </c>
     </row>
     <row r="135">
@@ -11535,7 +11679,7 @@
         <v>0.2537822299842412</v>
       </c>
       <c r="K135" s="6" t="n">
-        <v>0.2685927635260283</v>
+        <v>0.268513837001774</v>
       </c>
       <c r="L135" s="5" t="n">
         <v>3.6</v>
@@ -11546,14 +11690,14 @@
         </is>
       </c>
       <c r="N135" s="6" t="n">
-        <v>-0.01481053354178713</v>
+        <v>-0.01473160701753284</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="n">
         <v>15</v>
       </c>
       <c r="Q135" s="6" t="n">
-        <v>0.09071098079944635</v>
+        <v>0.09082830515486726</v>
       </c>
     </row>
     <row r="136">
@@ -11598,7 +11742,7 @@
         <v>0.3281718969442999</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0.2644824236079591</v>
+        <v>0.2644539006529559</v>
       </c>
       <c r="L136" s="3" t="n">
         <v>3.72</v>
@@ -11609,7 +11753,7 @@
         </is>
       </c>
       <c r="N136" s="4" t="n">
-        <v>0.06368947333634073</v>
+        <v>0.063717996291344</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -11620,7 +11764,7 @@
         <v>15</v>
       </c>
       <c r="Q136" s="4" t="n">
-        <v>0.09071098079944635</v>
+        <v>0.09082830515486726</v>
       </c>
     </row>
     <row r="137">
@@ -11665,7 +11809,7 @@
         <v>0.8010754395599823</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0.7258127722295252</v>
+        <v>0.7250307407688314</v>
       </c>
       <c r="L137" s="3" t="n">
         <v>1.3</v>
@@ -11676,7 +11820,7 @@
         </is>
       </c>
       <c r="N137" s="4" t="n">
-        <v>0.07526266733045706</v>
+        <v>0.07604469879115083</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -11687,7 +11831,7 @@
         <v>14</v>
       </c>
       <c r="Q137" s="4" t="n">
-        <v>0.09305771003049647</v>
+        <v>0.09422800001770826</v>
       </c>
     </row>
     <row r="138">
@@ -11732,7 +11876,7 @@
         <v>0.114055120689087</v>
       </c>
       <c r="K138" s="6" t="n">
-        <v>0.1679286676702215</v>
+        <v>0.1697323255868379</v>
       </c>
       <c r="L138" s="5" t="n">
         <v>6.25</v>
@@ -11743,14 +11887,14 @@
         </is>
       </c>
       <c r="N138" s="6" t="n">
-        <v>-0.05387354698113443</v>
+        <v>-0.0556772048977509</v>
       </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="n">
         <v>14</v>
       </c>
       <c r="Q138" s="6" t="n">
-        <v>0.09305771003049647</v>
+        <v>0.09422800001770826</v>
       </c>
     </row>
     <row r="139">
@@ -11795,7 +11939,7 @@
         <v>0.08486943975093079</v>
       </c>
       <c r="K139" s="6" t="n">
-        <v>0.1062585601002533</v>
+        <v>0.1052369336443306</v>
       </c>
       <c r="L139" s="5" t="n">
         <v>10</v>
@@ -11806,14 +11950,14 @@
         </is>
       </c>
       <c r="N139" s="6" t="n">
-        <v>-0.02138912034932255</v>
+        <v>-0.02036749389339981</v>
       </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="n">
         <v>14</v>
       </c>
       <c r="Q139" s="6" t="n">
-        <v>0.09305771003049647</v>
+        <v>0.09422800001770826</v>
       </c>
     </row>
     <row r="140">
@@ -12237,7 +12381,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 08:06 CAT</t>
+          <t>2026-10-25 11:17 CAT</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12418,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -12284,7 +12428,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99.90000000000001</v>
+        <v>100.08</v>
       </c>
     </row>
     <row r="8">
